--- a/job_application_forms/045_reemployment_interest_form--job_application_forms.xlsx
+++ b/job_application_forms/045_reemployment_interest_form--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>job_status</t>
+          <t>job_status_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Job Status</t>
+          <t>Job Status 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>job_title_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Job Title 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>job_id</t>
+          <t>job_id_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Job ID</t>
+          <t>Job Id 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_status_choices</t>
+          <t>job_status_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_status_choices</t>
+          <t>job_status_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_status_choices</t>
+          <t>job_status_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_status_choices</t>
+          <t>job_status_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
